--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Studio3/Desktop/PM Reports/Streamlit App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B7D248-E1AC-FB49-91E0-C2806E2B9983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC450659-2CF9-4F46-B990-03B92D31C26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16500" activeTab="1" xr2:uid="{C1D30A1A-AE12-9A4B-A39A-04F2223DCEBD}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="45720" windowHeight="23540" activeTab="1" xr2:uid="{C1D30A1A-AE12-9A4B-A39A-04F2223DCEBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="62" r:id="rId1"/>
@@ -1049,7 +1049,7 @@
       <name val="Gilroy-Regular"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1295,8 +1295,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="59">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1786,19 +1792,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1806,41 +1799,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -2016,6 +1974,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2065,7 +2047,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2229,15 +2211,6 @@
     <xf numFmtId="0" fontId="30" fillId="40" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2307,10 +2280,10 @@
     <xf numFmtId="0" fontId="34" fillId="43" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2323,24 +2296,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="44" fontId="34" fillId="43" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2377,13 +2332,13 @@
     <xf numFmtId="49" fontId="46" fillId="37" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="37" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="37" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="36" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="36" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="35" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="35" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="34" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2416,7 +2371,7 @@
     <xf numFmtId="49" fontId="34" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="43" fillId="40" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="40" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2431,28 +2386,28 @@
     <xf numFmtId="9" fontId="41" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="37" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="37" fillId="0" borderId="49" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="40" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="40" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="40" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="40" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2491,7 +2446,7 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2533,16 +2488,16 @@
     <xf numFmtId="0" fontId="47" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="34" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="34" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="34" fillId="43" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="34" fillId="43" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="34" fillId="43" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="34" fillId="43" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2551,10 +2506,10 @@
     <xf numFmtId="44" fontId="30" fillId="40" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2584,13 +2539,13 @@
     <xf numFmtId="0" fontId="39" fillId="42" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="42" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="42" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="42" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="42" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="42" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="42" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2617,6 +2572,12 @@
     <xf numFmtId="166" fontId="28" fillId="39" borderId="20" xfId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="49" fontId="30" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="34" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2640,12 +2601,6 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="42" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="42" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="35" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2686,8 +2641,71 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="44" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="44" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="44" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="56" xfId="44" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="44" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="44" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="34" fillId="44" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="44" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="44" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="46">
@@ -2738,27 +2756,7 @@
     <cellStyle name="Total" xfId="19" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="16" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="45">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="31">
     <dxf>
       <fill>
         <patternFill>
@@ -2965,368 +2963,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yy"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF01282A"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Gilroy-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF01282A"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3574,7 +3210,7 @@
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{58A4571A-A5EA-094F-BEE2-B8098FFBBF64}" name="Project Full Name"/>
     <tableColumn id="2" xr3:uid="{5F271DF8-2751-0345-9769-010C9BAEB476}" name="Transaction Type"/>
-    <tableColumn id="3" xr3:uid="{DDD55B90-6EE0-EE4B-9F39-BBD744621B53}" name="Expense Date" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{DDD55B90-6EE0-EE4B-9F39-BBD744621B53}" name="Expense Date" dataDxfId="30" totalsRowDxfId="29"/>
     <tableColumn id="4" xr3:uid="{78C0C915-36F7-A246-8E83-F6C9FFD9CF12}" name="Description"/>
     <tableColumn id="5" xr3:uid="{EB6D7488-7FCE-B94B-B2AD-5756AABDEF75}" name="Quantity"/>
     <tableColumn id="6" xr3:uid="{01D492C2-8A10-F54F-AE8B-C93ECBF74758}" name="Gross" totalsRowFunction="sum"/>
@@ -3589,28 +3225,6 @@
     <tableColumn id="15" xr3:uid="{CE468B0A-3546-F54A-8820-375857A1A264}" name="Expense Account Number"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E3898222-D4B7-084E-9341-AD4F4201E82E}" name="Table2" displayName="Table2" ref="B9:J14" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43" tableBorderDxfId="41" totalsRowBorderDxfId="40">
-  <autoFilter ref="B9:J14" xr:uid="{E3898222-D4B7-084E-9341-AD4F4201E82E}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{94E91729-501D-0B42-826B-8122B1520C52}" name="WMJ Code + Name" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{04817DB2-8900-304B-BE2B-DDD6C2AA7396}" name="Period of Performance" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{016AFB74-23F9-5B40-B34F-AD5179EB2C2F}" name="Total Labor_x000a_Award" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{FE941C46-3F8C-614D-9C61-D7C1D611D2DA}" name="Incurred _x000a_Labor Period of Performance" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{0929DCDE-F89B-CE4A-9D5E-D0FF11091DE1}" name="Incurred _x000a_Labor Project To Date" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{021F965E-2E12-DE48-88C9-23AD55A2A3A1}" name="Remaining _x000a_Labor" dataDxfId="34">
-      <calculatedColumnFormula>D10-F10</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{F1AA0EB8-CA0D-6E49-9B06-5403DD0FE5A9}" name="% Labor Utilized_x000a_(automated)" dataDxfId="0">
-      <calculatedColumnFormula>F10/D10</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{416943EB-7810-B54B-ADC1-F6F5CC1E6C83}" name="% Earned Value_x000a_(manual)" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{5AFAE1F3-23A5-AE4C-B79C-60642E6F7EAA}" name="Remaining Work / Flags" dataDxfId="32"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -73569,28 +73183,28 @@
   <sheetData>
     <row r="1" spans="1:15" ht="8" customHeight="1"/>
     <row r="2" spans="1:15" ht="15" customHeight="1">
-      <c r="B2" s="160" t="s">
+      <c r="B2" s="151" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1">
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
+      <c r="B3" s="151"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="151"/>
     </row>
     <row r="4" spans="1:15" ht="12" customHeight="1">
       <c r="B4" s="57"/>
@@ -73604,271 +73218,268 @@
       <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="16">
-      <c r="B5" s="136"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137" t="s">
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="138" t="s">
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
     </row>
     <row r="6" spans="1:15" ht="16">
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137" t="s">
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="138" t="s">
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="139">
+      <c r="I6" s="130">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="J6" s="136"/>
+      <c r="J6" s="127"/>
     </row>
     <row r="7" spans="1:15" ht="8" customHeight="1">
-      <c r="B7" s="136"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1">
-      <c r="B8" s="165" t="s">
+      <c r="B8" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
-      <c r="I8" s="165"/>
-      <c r="J8" s="165"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
+      <c r="H8" s="156"/>
+      <c r="I8" s="156"/>
+      <c r="J8" s="156"/>
     </row>
     <row r="9" spans="1:15" s="50" customFormat="1" ht="56" customHeight="1">
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="203" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="203" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="60" t="s">
+      <c r="E9" s="203" t="s">
         <v>144</v>
       </c>
-      <c r="F9" s="60" t="s">
+      <c r="F9" s="203" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="60" t="s">
+      <c r="G9" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="60" t="s">
+      <c r="H9" s="203" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="60" t="s">
+      <c r="I9" s="203" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="61" t="s">
+      <c r="J9" s="204" t="s">
         <v>32</v>
       </c>
       <c r="K9" s="53"/>
       <c r="L9" s="54"/>
     </row>
     <row r="10" spans="1:15" s="50" customFormat="1" ht="24" customHeight="1">
-      <c r="B10" s="91"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="212"/>
-      <c r="G10" s="93">
+      <c r="B10" s="205"/>
+      <c r="C10" s="206"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="208"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="207">
         <f t="shared" ref="G10:G14" si="0">D10-F10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="95" t="e">
+      <c r="H10" s="209" t="e">
         <f t="shared" ref="H10:H14" si="1">F10/D10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="95">
+      <c r="I10" s="209">
         <v>0</v>
       </c>
-      <c r="J10" s="92"/>
+      <c r="J10" s="210"/>
       <c r="K10" s="53"/>
       <c r="L10" s="54"/>
     </row>
     <row r="11" spans="1:15" ht="24" customHeight="1">
       <c r="A11" s="55"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="93">
+      <c r="B11" s="211"/>
+      <c r="C11" s="212"/>
+      <c r="D11" s="213"/>
+      <c r="E11" s="214"/>
+      <c r="F11" s="214"/>
+      <c r="G11" s="213">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="95" t="e">
+      <c r="H11" s="215" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="95">
+      <c r="I11" s="215">
         <v>0</v>
       </c>
-      <c r="J11" s="96"/>
+      <c r="J11" s="216"/>
     </row>
     <row r="12" spans="1:15" ht="24" customHeight="1">
       <c r="A12" s="55"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="92"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="93">
+      <c r="B12" s="205"/>
+      <c r="C12" s="206"/>
+      <c r="D12" s="207"/>
+      <c r="E12" s="217"/>
+      <c r="F12" s="217"/>
+      <c r="G12" s="207">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="95" t="e">
+      <c r="H12" s="209" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12" s="95">
+      <c r="I12" s="209">
         <v>0</v>
       </c>
-      <c r="J12" s="92"/>
+      <c r="J12" s="210"/>
     </row>
     <row r="13" spans="1:15" ht="24" customHeight="1">
-      <c r="B13" s="91"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="93">
+      <c r="B13" s="211"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="213"/>
+      <c r="E13" s="214"/>
+      <c r="F13" s="214"/>
+      <c r="G13" s="213">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="95" t="e">
+      <c r="H13" s="215" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I13" s="95">
+      <c r="I13" s="215">
         <v>0</v>
       </c>
-      <c r="J13" s="92"/>
+      <c r="J13" s="218"/>
     </row>
     <row r="14" spans="1:15" ht="24" customHeight="1">
       <c r="A14" s="55"/>
-      <c r="B14" s="91"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="93">
+      <c r="B14" s="219"/>
+      <c r="C14" s="220"/>
+      <c r="D14" s="221"/>
+      <c r="E14" s="222"/>
+      <c r="F14" s="222"/>
+      <c r="G14" s="221">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="95" t="e">
+      <c r="H14" s="223" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I14" s="95">
+      <c r="I14" s="223">
         <v>0</v>
       </c>
-      <c r="J14" s="96"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
+      <c r="J14" s="224"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
       <c r="O14" s="51"/>
     </row>
     <row r="15" spans="1:15" s="56" customFormat="1" ht="15">
-      <c r="B15" s="141" t="s">
+      <c r="B15" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="142"/>
-      <c r="D15" s="143">
-        <f>SUBTOTAL(109,Table2[Total Labor
-Award])</f>
+      <c r="C15" s="133"/>
+      <c r="D15" s="134">
+        <f>SUBTOTAL(109,'Account Overview'!$D$10:$D$14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="143">
-        <f>SUBTOTAL(109,Table2[Incurred 
-Labor Period of Performance])</f>
+      <c r="E15" s="134">
+        <f>SUBTOTAL(109,'Account Overview'!$E$10:$E$14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="143"/>
-      <c r="G15" s="143">
-        <f>SUBTOTAL(109,Table2[Remaining 
-Labor])</f>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134">
+        <f>SUBTOTAL(109,'Account Overview'!$G$10:$G$14)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="68" t="e">
+      <c r="H15" s="65" t="e">
         <f>(E15/D15)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I15" s="68" t="e">
+      <c r="I15" s="65" t="e">
         <f>((I10*D10)+(I11*D11)+(I12*D12)+(I13*D13)+(I14*D14))/D15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J15" s="141"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="89"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="86"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="B16" s="144"/>
-      <c r="C16" s="145"/>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="L16" s="87"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="L16" s="84"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="B17" s="144"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="146"/>
-      <c r="F17" s="146"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="144"/>
-      <c r="J17" s="144"/>
-      <c r="L17" s="87"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="L17" s="84"/>
     </row>
     <row r="18" spans="1:14" ht="19" customHeight="1">
-      <c r="B18" s="161" t="s">
+      <c r="B18" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="162"/>
-      <c r="D18" s="162"/>
-      <c r="E18" s="162"/>
-      <c r="F18" s="157"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="165" t="s">
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="148"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="165"/>
-      <c r="J18" s="136"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="83"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
     </row>
     <row r="19" spans="1:14" ht="20" customHeight="1">
       <c r="B19" s="58" t="s">
@@ -73877,154 +73488,154 @@
       <c r="C19" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="167" t="s">
+      <c r="D19" s="158" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="168"/>
-      <c r="F19" s="158"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="166">
+      <c r="E19" s="159"/>
+      <c r="F19" s="149"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="157">
         <f>E15+C20</f>
         <v>0</v>
       </c>
-      <c r="I19" s="166"/>
-      <c r="J19" s="136"/>
-      <c r="L19" s="87"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="127"/>
+      <c r="L19" s="84"/>
     </row>
     <row r="20" spans="1:14" ht="26" customHeight="1">
       <c r="A20" s="55"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="163"/>
-      <c r="E20" s="164"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="147"/>
-      <c r="H20" s="148"/>
-      <c r="I20" s="149"/>
-      <c r="J20" s="150"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="87"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="154"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="141"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="59"/>
     </row>
     <row r="22" spans="1:14" ht="15">
-      <c r="B22" s="65"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="B23" s="62"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="B24" s="62"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
     </row>
     <row r="25" spans="1:14" ht="15">
-      <c r="B25" s="65"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="B26" s="62"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="59"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="B27" s="62"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
     </row>
     <row r="28" spans="1:14" ht="15">
-      <c r="B28" s="65"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="B29" s="62"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="59"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="B30" s="62"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="59"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="B31" s="62"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -74037,24 +73648,21 @@
     <mergeCell ref="D19:E19"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:I14">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="between">
       <formula>0.5</formula>
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -74066,786 +73674,786 @@
   <dimension ref="B1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="2" style="156" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="156" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="156" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="156" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" style="156" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="156" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="156" customWidth="1"/>
-    <col min="8" max="11" width="14.83203125" style="156" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="156"/>
+    <col min="1" max="1" width="2" style="147" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="147" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="147" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="147" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" style="147" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="147" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="147" customWidth="1"/>
+    <col min="8" max="11" width="14.83203125" style="147" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="147"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" s="136" customFormat="1" ht="8" customHeight="1">
-      <c r="C1" s="140"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="152"/>
-    </row>
-    <row r="2" spans="2:11" s="136" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="160" t="s">
+    <row r="1" spans="2:11" s="127" customFormat="1" ht="8" customHeight="1">
+      <c r="C1" s="131"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="143"/>
+    </row>
+    <row r="2" spans="2:11" s="127" customFormat="1" ht="15" customHeight="1">
+      <c r="B2" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-    </row>
-    <row r="3" spans="2:11" s="136" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="160"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-    </row>
-    <row r="4" spans="2:11" s="136" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="153"/>
-      <c r="C4" s="153"/>
-      <c r="D4" s="153"/>
-      <c r="E4" s="153"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="153"/>
-      <c r="H4" s="154"/>
-      <c r="I4" s="153"/>
-      <c r="J4" s="153"/>
-      <c r="K4" s="153"/>
-    </row>
-    <row r="5" spans="2:11" s="136" customFormat="1" ht="16" customHeight="1">
-      <c r="B5" s="181" t="s">
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="151"/>
+    </row>
+    <row r="3" spans="2:11" s="127" customFormat="1" ht="15" customHeight="1">
+      <c r="B3" s="151"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="151"/>
+      <c r="K3" s="151"/>
+    </row>
+    <row r="4" spans="2:11" s="127" customFormat="1" ht="12" customHeight="1">
+      <c r="B4" s="144"/>
+      <c r="C4" s="144"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
+      <c r="F4" s="144"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="144"/>
+    </row>
+    <row r="5" spans="2:11" s="127" customFormat="1" ht="16" customHeight="1">
+      <c r="B5" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="181"/>
-      <c r="D5" s="69">
+      <c r="C5" s="172"/>
+      <c r="D5" s="66">
         <f>'Account Overview'!E5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="70" t="s">
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="69">
+      <c r="H5" s="66">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:11" s="136" customFormat="1" ht="17" customHeight="1">
-      <c r="B6" s="181" t="s">
+    <row r="6" spans="2:11" s="127" customFormat="1" ht="17" customHeight="1">
+      <c r="B6" s="172" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="181"/>
-      <c r="D6" s="69">
+      <c r="C6" s="172"/>
+      <c r="D6" s="66">
         <f>'Account Overview'!E6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="155"/>
-      <c r="F6" s="155"/>
-      <c r="G6" s="70" t="s">
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="135">
+      <c r="H6" s="126">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
     </row>
-    <row r="7" spans="2:11" s="136" customFormat="1" ht="8" customHeight="1" thickBot="1">
-      <c r="B7" s="69"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="155"/>
-      <c r="J7" s="151"/>
-      <c r="K7" s="152"/>
+    <row r="7" spans="2:11" s="127" customFormat="1" ht="8" customHeight="1" thickBot="1">
+      <c r="B7" s="66"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="146"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="143"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="175" t="s">
+      <c r="B8" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="176"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="177"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="175" t="s">
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="168"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="176"/>
-      <c r="I8" s="176"/>
-      <c r="J8" s="176"/>
-      <c r="K8" s="177"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="167"/>
+      <c r="J8" s="167"/>
+      <c r="K8" s="168"/>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="72">
+      <c r="C9" s="69">
         <v>46024</v>
       </c>
-      <c r="D9" s="73" t="s">
+      <c r="D9" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="74">
+      <c r="E9" s="71">
         <f>'Account Overview'!E10</f>
         <v>0</v>
       </c>
-      <c r="F9" s="69"/>
-      <c r="G9" s="130" t="s">
+      <c r="F9" s="66"/>
+      <c r="G9" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="131" t="s">
+      <c r="H9" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="132" t="s">
+      <c r="I9" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="133" t="s">
+      <c r="J9" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="134" t="s">
+      <c r="K9" s="125" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="76">
+      <c r="C10" s="73">
         <v>46100</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="77">
+      <c r="E10" s="74">
         <f ca="1">DATEDIF(C9,C11,"d")/7</f>
-        <v>17</v>
+        <v>17.428571428571427</v>
       </c>
-      <c r="F10" s="69"/>
-      <c r="G10" s="75" t="s">
+      <c r="F10" s="66"/>
+      <c r="G10" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="123"/>
-      <c r="I10" s="123"/>
-      <c r="J10" s="125">
+      <c r="H10" s="114"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="116">
         <f t="shared" ref="J10:J16" si="0">H10-I10</f>
         <v>0</v>
       </c>
-      <c r="K10" s="126">
+      <c r="K10" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="79">
+      <c r="C11" s="76">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="D11" s="70" t="s">
+      <c r="D11" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="77">
         <f ca="1">E9/E10</f>
         <v>0</v>
       </c>
-      <c r="F11" s="69"/>
-      <c r="G11" s="75" t="s">
+      <c r="F11" s="66"/>
+      <c r="G11" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="125">
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="169" t="s">
+      <c r="B12" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="170"/>
-      <c r="D12" s="73" t="s">
+      <c r="C12" s="161"/>
+      <c r="D12" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E12" s="71">
         <f>'Account Overview'!G10</f>
         <v>0</v>
       </c>
-      <c r="F12" s="69"/>
-      <c r="G12" s="75" t="s">
+      <c r="F12" s="66"/>
+      <c r="G12" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="124"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="125">
+      <c r="H12" s="115"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="126">
+      <c r="K12" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="171"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="69" t="s">
+      <c r="B13" s="162"/>
+      <c r="C13" s="163"/>
+      <c r="D13" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="77" t="e">
+      <c r="E13" s="74" t="e">
         <f ca="1">DATEDIF(C11,C10,"d")/7</f>
         <v>#NUM!</v>
       </c>
-      <c r="F13" s="69"/>
-      <c r="G13" s="75" t="s">
+      <c r="F13" s="66"/>
+      <c r="G13" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="124"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="125">
+      <c r="H13" s="115"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="126">
+      <c r="K13" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="17" thickBot="1">
-      <c r="B14" s="173"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="81" t="s">
+      <c r="B14" s="164"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="82" t="e">
+      <c r="E14" s="79" t="e">
         <f ca="1">E12/E13</f>
         <v>#NUM!</v>
       </c>
-      <c r="F14" s="69"/>
-      <c r="G14" s="75" t="s">
+      <c r="F14" s="66"/>
+      <c r="G14" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="124"/>
-      <c r="I14" s="123"/>
-      <c r="J14" s="125">
+      <c r="H14" s="115"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="126">
+      <c r="K14" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="15" customHeight="1">
-      <c r="B15" s="69"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="75" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="123"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="125">
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="126">
+      <c r="K15" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="F16" s="69"/>
-      <c r="G16" s="75" t="s">
+      <c r="F16" s="66"/>
+      <c r="G16" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="123"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="125">
+      <c r="H16" s="114"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="126">
+      <c r="K16" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="17" thickBot="1">
-      <c r="F17" s="69"/>
-      <c r="G17" s="128" t="s">
+      <c r="F17" s="66"/>
+      <c r="G17" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="129">
+      <c r="H17" s="120">
         <f>SUM(H10:H16)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="129">
+      <c r="I17" s="120">
         <f>SUM(I10:I16)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="129">
+      <c r="J17" s="120">
         <f>SUM(J10:J16)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="127">
+      <c r="K17" s="118">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="17" thickBot="1">
-      <c r="F18" s="69"/>
-      <c r="G18" s="155"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="146"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="175" t="s">
+      <c r="B19" s="166" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="176"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="177"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="175" t="s">
+      <c r="C19" s="167"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="166" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="176"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="176"/>
-      <c r="K19" s="177"/>
+      <c r="H19" s="167"/>
+      <c r="I19" s="167"/>
+      <c r="J19" s="167"/>
+      <c r="K19" s="168"/>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="72">
+      <c r="C20" s="69">
         <v>46024</v>
       </c>
-      <c r="D20" s="73" t="s">
+      <c r="D20" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="74">
+      <c r="E20" s="71">
         <f>'Account Overview'!E11</f>
         <v>0</v>
       </c>
-      <c r="F20" s="69"/>
-      <c r="G20" s="130" t="s">
+      <c r="F20" s="66"/>
+      <c r="G20" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="131" t="s">
+      <c r="H20" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="132" t="s">
+      <c r="I20" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="133" t="s">
+      <c r="J20" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="K20" s="134" t="s">
+      <c r="K20" s="125" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="76">
+      <c r="C21" s="73">
         <v>46100</v>
       </c>
-      <c r="D21" s="69" t="s">
+      <c r="D21" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="77">
+      <c r="E21" s="74">
         <f ca="1">DATEDIF(C20,C22,"d")/7</f>
-        <v>17</v>
+        <v>17.428571428571427</v>
       </c>
-      <c r="F21" s="69"/>
-      <c r="G21" s="75" t="s">
+      <c r="F21" s="66"/>
+      <c r="G21" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="H21" s="123"/>
-      <c r="I21" s="123"/>
-      <c r="J21" s="125">
+      <c r="H21" s="114"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="116">
         <f t="shared" ref="J21:J27" si="1">H21-I21</f>
         <v>0</v>
       </c>
-      <c r="K21" s="126">
+      <c r="K21" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="79">
+      <c r="C22" s="76">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="D22" s="70" t="s">
+      <c r="D22" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="80">
+      <c r="E22" s="77">
         <f ca="1">E20/E21</f>
         <v>0</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="75" t="s">
+      <c r="F22" s="66"/>
+      <c r="G22" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="123"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="125">
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="126">
+      <c r="K22" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="169" t="s">
+      <c r="B23" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="170"/>
-      <c r="D23" s="73" t="s">
+      <c r="C23" s="161"/>
+      <c r="D23" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="74">
+      <c r="E23" s="71">
         <f>'Account Overview'!G11</f>
         <v>0</v>
       </c>
-      <c r="G23" s="75" t="s">
+      <c r="G23" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="H23" s="124"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="125">
+      <c r="H23" s="115"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="126">
+      <c r="K23" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="171"/>
-      <c r="C24" s="172"/>
-      <c r="D24" s="69" t="s">
+      <c r="B24" s="162"/>
+      <c r="C24" s="163"/>
+      <c r="D24" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="77" t="e">
+      <c r="E24" s="74" t="e">
         <f ca="1">DATEDIF(C22,C21,"d")/7</f>
         <v>#NUM!</v>
       </c>
-      <c r="G24" s="75" t="s">
+      <c r="G24" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="124"/>
-      <c r="I24" s="123"/>
-      <c r="J24" s="125">
+      <c r="H24" s="115"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="126">
+      <c r="K24" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="17" thickBot="1">
-      <c r="B25" s="173"/>
-      <c r="C25" s="174"/>
-      <c r="D25" s="81" t="s">
+      <c r="B25" s="164"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="82" t="e">
+      <c r="E25" s="79" t="e">
         <f ca="1">E23/E24</f>
         <v>#NUM!</v>
       </c>
-      <c r="G25" s="75" t="s">
+      <c r="G25" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="124"/>
-      <c r="I25" s="123"/>
-      <c r="J25" s="125">
+      <c r="H25" s="115"/>
+      <c r="I25" s="114"/>
+      <c r="J25" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="126">
+      <c r="K25" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:11">
-      <c r="G26" s="75" t="s">
+      <c r="G26" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="125">
+      <c r="H26" s="114"/>
+      <c r="I26" s="114"/>
+      <c r="J26" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="126">
+      <c r="K26" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="G27" s="75" t="s">
+      <c r="G27" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="123"/>
-      <c r="I27" s="123"/>
-      <c r="J27" s="125">
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+      <c r="J27" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="126">
+      <c r="K27" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:11" ht="17" thickBot="1">
-      <c r="G28" s="128" t="s">
+      <c r="G28" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="129">
+      <c r="H28" s="120">
         <f>SUM(H21:H27)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="129">
+      <c r="I28" s="120">
         <f>SUM(I21:I27)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="129">
+      <c r="J28" s="120">
         <f>SUM(J21:J27)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="127" t="e">
+      <c r="K28" s="118" t="e">
         <f>((K21*H21)+(K22*H22)+(K23*H23)+(K24*H24)+(K25*H25)+(K26*H26)+(K27*H27))/H28</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="17" thickBot="1"/>
     <row r="30" spans="2:11">
-      <c r="B30" s="178" t="s">
+      <c r="B30" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="180"/>
-      <c r="G30" s="175" t="s">
+      <c r="C30" s="170"/>
+      <c r="D30" s="170"/>
+      <c r="E30" s="171"/>
+      <c r="G30" s="166" t="s">
         <v>64</v>
       </c>
-      <c r="H30" s="176"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="176"/>
-      <c r="K30" s="177"/>
+      <c r="H30" s="167"/>
+      <c r="I30" s="167"/>
+      <c r="J30" s="167"/>
+      <c r="K30" s="168"/>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="71" t="s">
+      <c r="B31" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="72">
+      <c r="C31" s="69">
         <v>45818</v>
       </c>
-      <c r="D31" s="73" t="s">
+      <c r="D31" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="74">
+      <c r="E31" s="71">
         <f>'Account Overview'!E12</f>
         <v>0</v>
       </c>
-      <c r="G31" s="130" t="s">
+      <c r="G31" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="131" t="s">
+      <c r="H31" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="I31" s="132" t="s">
+      <c r="I31" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="J31" s="133" t="s">
+      <c r="J31" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="K31" s="134" t="s">
+      <c r="K31" s="125" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="32" spans="2:11">
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="76">
+      <c r="C32" s="73">
         <v>46106</v>
       </c>
-      <c r="D32" s="69" t="s">
+      <c r="D32" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="77">
+      <c r="E32" s="74">
         <f ca="1">DATEDIF(C31,C33,"d")/7</f>
-        <v>46.428571428571431</v>
+        <v>46.857142857142854</v>
       </c>
-      <c r="G32" s="75" t="s">
+      <c r="G32" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="H32" s="123"/>
-      <c r="I32" s="123"/>
-      <c r="J32" s="125">
+      <c r="H32" s="114"/>
+      <c r="I32" s="114"/>
+      <c r="J32" s="116">
         <f t="shared" ref="J32:J38" si="2">H32-I32</f>
         <v>0</v>
       </c>
-      <c r="K32" s="126">
+      <c r="K32" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:11">
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="79">
+      <c r="C33" s="76">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="80">
+      <c r="E33" s="77">
         <f ca="1">E31/E32</f>
         <v>0</v>
       </c>
-      <c r="G33" s="75" t="s">
+      <c r="G33" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="123"/>
-      <c r="I33" s="123"/>
-      <c r="J33" s="125">
+      <c r="H33" s="114"/>
+      <c r="I33" s="114"/>
+      <c r="J33" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K33" s="126">
+      <c r="K33" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="169" t="s">
+      <c r="B34" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="170"/>
-      <c r="D34" s="73" t="s">
+      <c r="C34" s="161"/>
+      <c r="D34" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="74">
+      <c r="E34" s="71">
         <f>'Account Overview'!G12</f>
         <v>0</v>
       </c>
-      <c r="G34" s="75" t="s">
+      <c r="G34" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="H34" s="124"/>
-      <c r="I34" s="123"/>
-      <c r="J34" s="125">
+      <c r="H34" s="115"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K34" s="126">
+      <c r="K34" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:11">
-      <c r="B35" s="171"/>
-      <c r="C35" s="172"/>
-      <c r="D35" s="69" t="s">
+      <c r="B35" s="162"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="77" t="e">
+      <c r="E35" s="74" t="e">
         <f ca="1">DATEDIF(C33,C32,"d")/7</f>
         <v>#NUM!</v>
       </c>
-      <c r="G35" s="75" t="s">
+      <c r="G35" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="H35" s="124"/>
-      <c r="I35" s="123"/>
-      <c r="J35" s="125">
+      <c r="H35" s="115"/>
+      <c r="I35" s="114"/>
+      <c r="J35" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="126">
+      <c r="K35" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:11" ht="17" thickBot="1">
-      <c r="B36" s="173"/>
-      <c r="C36" s="174"/>
-      <c r="D36" s="81" t="s">
+      <c r="B36" s="164"/>
+      <c r="C36" s="165"/>
+      <c r="D36" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="82" t="e">
+      <c r="E36" s="79" t="e">
         <f ca="1">E34/E35</f>
         <v>#NUM!</v>
       </c>
-      <c r="G36" s="75" t="s">
+      <c r="G36" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="H36" s="124"/>
-      <c r="I36" s="123"/>
-      <c r="J36" s="125">
+      <c r="H36" s="115"/>
+      <c r="I36" s="114"/>
+      <c r="J36" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="126">
+      <c r="K36" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:11">
-      <c r="G37" s="75" t="s">
+      <c r="G37" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="123"/>
-      <c r="I37" s="123"/>
-      <c r="J37" s="125">
+      <c r="H37" s="114"/>
+      <c r="I37" s="114"/>
+      <c r="J37" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="126">
+      <c r="K37" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:11">
-      <c r="G38" s="75" t="s">
+      <c r="G38" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="H38" s="123"/>
-      <c r="I38" s="123"/>
-      <c r="J38" s="125">
+      <c r="H38" s="114"/>
+      <c r="I38" s="114"/>
+      <c r="J38" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K38" s="126">
+      <c r="K38" s="117">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="17" thickBot="1">
-      <c r="G39" s="128" t="s">
+      <c r="G39" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="H39" s="129">
+      <c r="H39" s="120">
         <f>SUM(H32:H38)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="129">
+      <c r="I39" s="120">
         <f>SUM(I32:I38)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="129">
+      <c r="J39" s="120">
         <f>SUM(J32:J38)</f>
         <v>0</v>
       </c>
-      <c r="K39" s="127">
+      <c r="K39" s="118">
         <v>0</v>
       </c>
     </row>
@@ -74865,7 +74473,7 @@
     <mergeCell ref="B12:C14"/>
   </mergeCells>
   <conditionalFormatting sqref="J10:J17 J21:J28 J32:J39">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -74925,7 +74533,7 @@
       </c>
       <c r="E3" s="12">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="13" t="s">
@@ -74973,12 +74581,12 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="19" thickBot="1">
-      <c r="B6" s="184" t="s">
+      <c r="B6" s="175" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
+      <c r="C6" s="175"/>
+      <c r="D6" s="175"/>
+      <c r="E6" s="175"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -75013,12 +74621,12 @@
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="2:9" ht="19" thickBot="1">
-      <c r="B9" s="184" t="s">
+      <c r="B9" s="175" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="175"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -75134,12 +74742,12 @@
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="2:9" ht="19" thickBot="1">
-      <c r="B18" s="184" t="s">
+      <c r="B18" s="175" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="184"/>
-      <c r="D18" s="184"/>
-      <c r="E18" s="184"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="175"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -75152,10 +74760,10 @@
       <c r="C19" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="185" t="s">
+      <c r="D19" s="176" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="186"/>
+      <c r="E19" s="177"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -75168,10 +74776,10 @@
       <c r="C20" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="187" t="s">
+      <c r="D20" s="178" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="188"/>
+      <c r="E20" s="179"/>
     </row>
     <row r="21" spans="2:9" ht="43" customHeight="1" thickBot="1">
       <c r="B21" s="33" t="s">
@@ -75180,10 +74788,10 @@
       <c r="C21" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="182" t="s">
+      <c r="D21" s="173" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="183"/>
+      <c r="E21" s="174"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -75206,311 +74814,312 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
-    <col min="5" max="5" width="43" style="102" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="102"/>
+    <col min="1" max="1" width="3.83203125" style="93" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="93" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="93" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="93" customWidth="1"/>
+    <col min="5" max="5" width="43" style="93" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="93" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="93" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="93" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="93" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
-      <c r="C1" s="63"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="98"/>
-    </row>
-    <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="195" t="s">
+    <row r="1" spans="2:10" s="59" customFormat="1" ht="8" customHeight="1">
+      <c r="C1" s="60"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="89"/>
+    </row>
+    <row r="2" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B2" s="188" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="98"/>
-    </row>
-    <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="195"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="195"/>
-      <c r="I3" s="195"/>
-      <c r="J3" s="98"/>
-    </row>
-    <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="98"/>
-    </row>
-    <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="100" t="s">
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="89"/>
+    </row>
+    <row r="3" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B3" s="188"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="188"/>
+      <c r="I3" s="188"/>
+      <c r="J3" s="89"/>
+    </row>
+    <row r="4" spans="2:10" s="59" customFormat="1" ht="12" customHeight="1">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="89"/>
+    </row>
+    <row r="5" spans="2:10" s="59" customFormat="1">
+      <c r="B5" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="101">
+      <c r="E5" s="92">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="210"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="98"/>
-    </row>
-    <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="100" t="s">
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="89"/>
+    </row>
+    <row r="6" spans="2:10" s="59" customFormat="1">
+      <c r="B6" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="59">
         <f>'Account Overview'!E6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="97">
+      <c r="E6" s="88">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="H6" s="210"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="98"/>
-    </row>
-    <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
-      <c r="C7" s="63"/>
-      <c r="H7" s="210"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="98"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="89"/>
+    </row>
+    <row r="7" spans="2:10" s="59" customFormat="1" ht="10" customHeight="1">
+      <c r="C7" s="60"/>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="202"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="199" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="209"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="199"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="200"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="207" t="s">
+      <c r="B11" s="198" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="207"/>
-      <c r="D11" s="207"/>
-      <c r="E11" s="207"/>
+      <c r="C11" s="198"/>
+      <c r="D11" s="198"/>
+      <c r="E11" s="198"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="115" t="s">
+      <c r="B12" s="106" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="197" t="s">
+      <c r="D12" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="198"/>
-      <c r="G12" s="122" t="s">
+      <c r="E12" s="181"/>
+      <c r="G12" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="122" t="s">
+      <c r="I12" s="113" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="105" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="189" t="s">
+      <c r="D13" s="182" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="190"/>
-      <c r="G13" s="109" t="s">
+      <c r="E13" s="183"/>
+      <c r="G13" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="109" t="s">
+      <c r="I13" s="100" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="203" t="s">
+      <c r="D14" s="194" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="204"/>
-      <c r="G14" s="110" t="s">
+      <c r="E14" s="195"/>
+      <c r="G14" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="110" t="s">
+      <c r="I14" s="101" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="189" t="s">
+      <c r="D15" s="182" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="190"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="111" t="s">
+      <c r="E15" s="183"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="111" t="s">
+      <c r="I15" s="102" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="203" t="s">
+      <c r="D16" s="194" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="204"/>
-      <c r="F16" s="107"/>
-      <c r="H16" s="107"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="98"/>
+      <c r="H16" s="98"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="105" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="205" t="s">
+      <c r="D17" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="206"/>
-      <c r="F17" s="107"/>
-      <c r="H17" s="107"/>
+      <c r="E17" s="197"/>
+      <c r="F17" s="98"/>
+      <c r="H17" s="98"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="118" t="s">
+      <c r="B18" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="108" t="s">
+      <c r="C18" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="201" t="s">
+      <c r="D18" s="192" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="202"/>
-      <c r="F18" s="107"/>
-      <c r="H18" s="107"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="98"/>
+      <c r="H18" s="98"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="105"/>
+      <c r="E19" s="96"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="196" t="s">
+      <c r="B20" s="189" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="196"/>
+      <c r="C20" s="189"/>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="115" t="s">
+      <c r="B21" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="116" t="s">
+      <c r="C21" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="197" t="s">
+      <c r="D21" s="180" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="198"/>
+      <c r="E21" s="181"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="104" t="s">
+      <c r="C22" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="199" t="s">
+      <c r="D22" s="190" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="200"/>
+      <c r="E22" s="191"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="120" t="s">
+      <c r="B23" s="111" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="191" t="s">
+      <c r="D23" s="184" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="192"/>
+      <c r="E23" s="185"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="110" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="193" t="s">
+      <c r="D24" s="186" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="194"/>
+      <c r="E24" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B8:G8"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D23:E23"/>
@@ -75527,29 +75136,28 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D9:I9"/>
     <mergeCell ref="H5:I8"/>
-    <mergeCell ref="B8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="At Risk">
+    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="At Risk">
       <formula>NOT(ISERROR(SEARCH("At Risk",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="HEALTHY">
+    <cfRule type="containsText" dxfId="22" priority="6" operator="containsText" text="HEALTHY">
       <formula>NOT(ISERROR(SEARCH("HEALTHY",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24 C9">
-    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="Progress Halted">
+    <cfRule type="containsText" dxfId="21" priority="4" operator="containsText" text="Progress Halted">
       <formula>NOT(ISERROR(SEARCH("Progress Halted",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="Over">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Over">
       <formula>NOT(ISERROR(SEARCH("Over",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="On">
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="On">
       <formula>NOT(ISERROR(SEARCH("On",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="Under">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Under">
       <formula>NOT(ISERROR(SEARCH("Under",C13)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -75574,311 +75182,316 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
-    <col min="5" max="5" width="43" style="102" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="102"/>
+    <col min="1" max="1" width="3.83203125" style="93" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="93" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="93" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="93" customWidth="1"/>
+    <col min="5" max="5" width="43" style="93" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="93" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="93" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="93" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="93" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
-      <c r="C1" s="63"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="98"/>
-    </row>
-    <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="195" t="s">
+    <row r="1" spans="2:10" s="59" customFormat="1" ht="8" customHeight="1">
+      <c r="C1" s="60"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="89"/>
+    </row>
+    <row r="2" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B2" s="188" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="98"/>
-    </row>
-    <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="195"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="195"/>
-      <c r="I3" s="195"/>
-      <c r="J3" s="98"/>
-    </row>
-    <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="98"/>
-    </row>
-    <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="100" t="s">
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="89"/>
+    </row>
+    <row r="3" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B3" s="188"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="188"/>
+      <c r="I3" s="188"/>
+      <c r="J3" s="89"/>
+    </row>
+    <row r="4" spans="2:10" s="59" customFormat="1" ht="12" customHeight="1">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="89"/>
+    </row>
+    <row r="5" spans="2:10" s="59" customFormat="1">
+      <c r="B5" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="101">
+      <c r="E5" s="92">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="210"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="98"/>
-    </row>
-    <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="100" t="s">
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="89"/>
+    </row>
+    <row r="6" spans="2:10" s="59" customFormat="1">
+      <c r="B6" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="59">
         <f>'Account Overview'!E6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="97">
+      <c r="E6" s="88">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="H6" s="210"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="98"/>
-    </row>
-    <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
-      <c r="C7" s="63"/>
-      <c r="H7" s="210"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="98"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="89"/>
+    </row>
+    <row r="7" spans="2:10" s="59" customFormat="1" ht="10" customHeight="1">
+      <c r="C7" s="60"/>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="202"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="199" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="209"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="199"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="200"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="207" t="s">
+      <c r="B11" s="198" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="207"/>
-      <c r="D11" s="207"/>
-      <c r="E11" s="207"/>
+      <c r="C11" s="198"/>
+      <c r="D11" s="198"/>
+      <c r="E11" s="198"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="115" t="s">
+      <c r="B12" s="106" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="197" t="s">
+      <c r="D12" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="198"/>
-      <c r="G12" s="122" t="s">
+      <c r="E12" s="181"/>
+      <c r="G12" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="122" t="s">
+      <c r="I12" s="113" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="105" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="189" t="s">
+      <c r="D13" s="182" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="190"/>
-      <c r="G13" s="109" t="s">
+      <c r="E13" s="183"/>
+      <c r="G13" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="109" t="s">
+      <c r="I13" s="100" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="203" t="s">
+      <c r="D14" s="194" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="204"/>
-      <c r="G14" s="110" t="s">
+      <c r="E14" s="195"/>
+      <c r="G14" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="110" t="s">
+      <c r="I14" s="101" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="189" t="s">
+      <c r="D15" s="182" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="190"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="111" t="s">
+      <c r="E15" s="183"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="111" t="s">
+      <c r="I15" s="102" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="203" t="s">
+      <c r="D16" s="194" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="204"/>
-      <c r="F16" s="107"/>
-      <c r="H16" s="107"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="98"/>
+      <c r="H16" s="98"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="105" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="205" t="s">
+      <c r="D17" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="206"/>
-      <c r="F17" s="107"/>
-      <c r="H17" s="107"/>
+      <c r="E17" s="197"/>
+      <c r="F17" s="98"/>
+      <c r="H17" s="98"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="118" t="s">
+      <c r="B18" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="108" t="s">
+      <c r="C18" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="201" t="s">
+      <c r="D18" s="192" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="202"/>
-      <c r="F18" s="107"/>
-      <c r="H18" s="107"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="98"/>
+      <c r="H18" s="98"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="105"/>
+      <c r="E19" s="96"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="196" t="s">
+      <c r="B20" s="189" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="196"/>
+      <c r="C20" s="189"/>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="115" t="s">
+      <c r="B21" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="116" t="s">
+      <c r="C21" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="197" t="s">
+      <c r="D21" s="180" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="198"/>
+      <c r="E21" s="181"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="104" t="s">
+      <c r="C22" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="199" t="s">
+      <c r="D22" s="190" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="200"/>
+      <c r="E22" s="191"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="120" t="s">
+      <c r="B23" s="111" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="191" t="s">
+      <c r="D23" s="184" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="192"/>
+      <c r="E23" s="185"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="110" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="193" t="s">
+      <c r="D24" s="186" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="194"/>
+      <c r="E24" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="B2:I3"/>
@@ -75891,33 +75504,28 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="At Risk">
+    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="At Risk">
       <formula>NOT(ISERROR(SEARCH("At Risk",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="HEALTHY">
+    <cfRule type="containsText" dxfId="16" priority="6" operator="containsText" text="HEALTHY">
       <formula>NOT(ISERROR(SEARCH("HEALTHY",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24 C9">
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Progress Halted">
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="Progress Halted">
       <formula>NOT(ISERROR(SEARCH("Progress Halted",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="Over">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Over">
       <formula>NOT(ISERROR(SEARCH("Over",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="On">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="On">
       <formula>NOT(ISERROR(SEARCH("On",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Under">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Under">
       <formula>NOT(ISERROR(SEARCH("Under",C13)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -75942,311 +75550,316 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
-    <col min="5" max="5" width="43" style="102" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="102"/>
+    <col min="1" max="1" width="3.83203125" style="93" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="93" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="93" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="93" customWidth="1"/>
+    <col min="5" max="5" width="43" style="93" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="93" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="93" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="93" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="93" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
-      <c r="C1" s="63"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="98"/>
-    </row>
-    <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="195" t="s">
+    <row r="1" spans="2:10" s="59" customFormat="1" ht="8" customHeight="1">
+      <c r="C1" s="60"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="89"/>
+    </row>
+    <row r="2" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B2" s="188" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="98"/>
-    </row>
-    <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="195"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="195"/>
-      <c r="I3" s="195"/>
-      <c r="J3" s="98"/>
-    </row>
-    <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="98"/>
-    </row>
-    <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="100" t="s">
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="89"/>
+    </row>
+    <row r="3" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B3" s="188"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="188"/>
+      <c r="I3" s="188"/>
+      <c r="J3" s="89"/>
+    </row>
+    <row r="4" spans="2:10" s="59" customFormat="1" ht="12" customHeight="1">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="89"/>
+    </row>
+    <row r="5" spans="2:10" s="59" customFormat="1">
+      <c r="B5" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="101">
+      <c r="E5" s="92">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="210"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="98"/>
-    </row>
-    <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="100" t="s">
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="89"/>
+    </row>
+    <row r="6" spans="2:10" s="59" customFormat="1">
+      <c r="B6" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="59">
         <f>'Account Overview'!E6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="97">
+      <c r="E6" s="88">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="H6" s="210"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="98"/>
-    </row>
-    <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
-      <c r="C7" s="63"/>
-      <c r="H7" s="210"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="98"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="89"/>
+    </row>
+    <row r="7" spans="2:10" s="59" customFormat="1" ht="10" customHeight="1">
+      <c r="C7" s="60"/>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="202"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="199" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="209"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="199"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="200"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="207" t="s">
+      <c r="B11" s="198" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="207"/>
-      <c r="D11" s="207"/>
-      <c r="E11" s="207"/>
+      <c r="C11" s="198"/>
+      <c r="D11" s="198"/>
+      <c r="E11" s="198"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="115" t="s">
+      <c r="B12" s="106" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="197" t="s">
+      <c r="D12" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="198"/>
-      <c r="G12" s="122" t="s">
+      <c r="E12" s="181"/>
+      <c r="G12" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="122" t="s">
+      <c r="I12" s="113" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="105" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="189" t="s">
+      <c r="D13" s="182" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="190"/>
-      <c r="G13" s="109" t="s">
+      <c r="E13" s="183"/>
+      <c r="G13" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="109" t="s">
+      <c r="I13" s="100" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="203" t="s">
+      <c r="D14" s="194" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="204"/>
-      <c r="G14" s="110" t="s">
+      <c r="E14" s="195"/>
+      <c r="G14" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="110" t="s">
+      <c r="I14" s="101" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="189" t="s">
+      <c r="D15" s="182" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="190"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="111" t="s">
+      <c r="E15" s="183"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="111" t="s">
+      <c r="I15" s="102" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="203" t="s">
+      <c r="D16" s="194" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="204"/>
-      <c r="F16" s="107"/>
-      <c r="H16" s="107"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="98"/>
+      <c r="H16" s="98"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="105" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="205" t="s">
+      <c r="D17" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="206"/>
-      <c r="F17" s="107"/>
-      <c r="H17" s="107"/>
+      <c r="E17" s="197"/>
+      <c r="F17" s="98"/>
+      <c r="H17" s="98"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="118" t="s">
+      <c r="B18" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="108" t="s">
+      <c r="C18" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="201" t="s">
+      <c r="D18" s="192" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="202"/>
-      <c r="F18" s="107"/>
-      <c r="H18" s="107"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="98"/>
+      <c r="H18" s="98"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="105"/>
+      <c r="E19" s="96"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="196" t="s">
+      <c r="B20" s="189" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="196"/>
+      <c r="C20" s="189"/>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="115" t="s">
+      <c r="B21" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="116" t="s">
+      <c r="C21" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="197" t="s">
+      <c r="D21" s="180" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="198"/>
+      <c r="E21" s="181"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="104" t="s">
+      <c r="C22" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="199" t="s">
+      <c r="D22" s="190" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="200"/>
+      <c r="E22" s="191"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="120" t="s">
+      <c r="B23" s="111" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="191" t="s">
+      <c r="D23" s="184" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="192"/>
+      <c r="E23" s="185"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="110" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="193" t="s">
+      <c r="D24" s="186" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="194"/>
+      <c r="E24" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="B2:I3"/>
@@ -76259,33 +75872,28 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="At Risk">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="At Risk">
       <formula>NOT(ISERROR(SEARCH("At Risk",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="HEALTHY">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="HEALTHY">
       <formula>NOT(ISERROR(SEARCH("HEALTHY",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24 C9">
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Progress Halted">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="Progress Halted">
       <formula>NOT(ISERROR(SEARCH("Progress Halted",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="Over">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Over">
       <formula>NOT(ISERROR(SEARCH("Over",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="On">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="On">
       <formula>NOT(ISERROR(SEARCH("On",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="Under">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Under">
       <formula>NOT(ISERROR(SEARCH("Under",C13)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76310,315 +75918,320 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
-    <col min="5" max="5" width="43" style="102" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="102"/>
+    <col min="1" max="1" width="3.83203125" style="93" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="93" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="93" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="93" customWidth="1"/>
+    <col min="5" max="5" width="43" style="93" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="93" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="93" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="93" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="93" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
-      <c r="C1" s="63"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="98"/>
-    </row>
-    <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="195" t="s">
+    <row r="1" spans="2:10" s="59" customFormat="1" ht="8" customHeight="1">
+      <c r="C1" s="60"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="89"/>
+    </row>
+    <row r="2" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B2" s="188" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="195"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="98"/>
-    </row>
-    <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="195"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="195"/>
-      <c r="I3" s="195"/>
-      <c r="J3" s="98"/>
-    </row>
-    <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="98"/>
-    </row>
-    <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="100" t="s">
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="188"/>
+      <c r="J2" s="89"/>
+    </row>
+    <row r="3" spans="2:10" s="59" customFormat="1" ht="15" customHeight="1">
+      <c r="B3" s="188"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="188"/>
+      <c r="I3" s="188"/>
+      <c r="J3" s="89"/>
+    </row>
+    <row r="4" spans="2:10" s="59" customFormat="1" ht="12" customHeight="1">
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="89"/>
+    </row>
+    <row r="5" spans="2:10" s="59" customFormat="1">
+      <c r="B5" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="59">
         <f>'Account Overview'!E5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="101">
+      <c r="E5" s="92">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="210"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="98"/>
-    </row>
-    <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="100" t="s">
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+      <c r="J5" s="89"/>
+    </row>
+    <row r="6" spans="2:10" s="59" customFormat="1">
+      <c r="B6" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="59">
         <f>'Account Overview'!E6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="97">
+      <c r="E6" s="88">
         <f ca="1">TODAY()</f>
-        <v>46143</v>
+        <v>46146</v>
       </c>
-      <c r="H6" s="210"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="98"/>
-    </row>
-    <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
-      <c r="C7" s="63"/>
-      <c r="H7" s="210"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="98"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="89"/>
+    </row>
+    <row r="7" spans="2:10" s="59" customFormat="1" ht="10" customHeight="1">
+      <c r="C7" s="60"/>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
+      <c r="J7" s="89"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
-      <c r="G8" s="207"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="202"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="208" t="s">
+      <c r="D9" s="199" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="208"/>
-      <c r="I9" s="209"/>
+      <c r="E9" s="199"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="199"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="200"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="207" t="s">
+      <c r="B11" s="198" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="207"/>
-      <c r="D11" s="207"/>
-      <c r="E11" s="207"/>
+      <c r="C11" s="198"/>
+      <c r="D11" s="198"/>
+      <c r="E11" s="198"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="115" t="s">
+      <c r="B12" s="106" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="116" t="s">
+      <c r="C12" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="197" t="s">
+      <c r="D12" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="198"/>
-      <c r="G12" s="122" t="s">
+      <c r="E12" s="181"/>
+      <c r="G12" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="122" t="s">
+      <c r="I12" s="113" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="105" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="104" t="s">
+      <c r="C13" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="189" t="s">
+      <c r="D13" s="182" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="190"/>
-      <c r="G13" s="109" t="s">
+      <c r="E13" s="183"/>
+      <c r="G13" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="109" t="s">
+      <c r="I13" s="100" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="203" t="s">
+      <c r="D14" s="194" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="204"/>
-      <c r="G14" s="110" t="s">
+      <c r="E14" s="195"/>
+      <c r="G14" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="110" t="s">
+      <c r="I14" s="101" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="104" t="s">
+      <c r="C15" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="189" t="s">
+      <c r="D15" s="182" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="190"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="111" t="s">
+      <c r="E15" s="183"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="111" t="s">
+      <c r="I15" s="102" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="108" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="203" t="s">
+      <c r="D16" s="194" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="204"/>
-      <c r="F16" s="107"/>
-      <c r="H16" s="107"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="98"/>
+      <c r="H16" s="98"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="105" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="205" t="s">
+      <c r="D17" s="196" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="206"/>
-      <c r="F17" s="107"/>
-      <c r="H17" s="107"/>
+      <c r="E17" s="197"/>
+      <c r="F17" s="98"/>
+      <c r="H17" s="98"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="118" t="s">
+      <c r="B18" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="108" t="s">
+      <c r="C18" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="201" t="s">
+      <c r="D18" s="192" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="202"/>
-      <c r="F18" s="107"/>
-      <c r="H18" s="107"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="98"/>
+      <c r="H18" s="98"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="105"/>
+      <c r="E19" s="96"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="196" t="s">
+      <c r="B20" s="189" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="196"/>
+      <c r="C20" s="189"/>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="115" t="s">
+      <c r="B21" s="106" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="116" t="s">
+      <c r="C21" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="197" t="s">
+      <c r="D21" s="180" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="198"/>
+      <c r="E21" s="181"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="104" t="s">
+      <c r="C22" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="199" t="s">
+      <c r="D22" s="190" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="200"/>
+      <c r="E22" s="191"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="120" t="s">
+      <c r="B23" s="111" t="s">
         <v>140</v>
       </c>
-      <c r="C23" s="104" t="s">
+      <c r="C23" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="191" t="s">
+      <c r="D23" s="184" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="192"/>
+      <c r="E23" s="185"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="110" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="193" t="s">
+      <c r="D24" s="186" t="s">
         <v>143</v>
       </c>
-      <c r="E24" s="194"/>
+      <c r="E24" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="B2:I3"/>
@@ -76631,33 +76244,28 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="At Risk">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="At Risk">
       <formula>NOT(ISERROR(SEARCH("At Risk",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="HEALTHY">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="HEALTHY">
       <formula>NOT(ISERROR(SEARCH("HEALTHY",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24 C9">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Progress Halted">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Progress Halted">
       <formula>NOT(ISERROR(SEARCH("Progress Halted",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:C18 C22:C24">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Over">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Over">
       <formula>NOT(ISERROR(SEARCH("Over",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="On">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="On">
       <formula>NOT(ISERROR(SEARCH("On",C13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Under">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Under">
       <formula>NOT(ISERROR(SEARCH("Under",C13)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -76675,6 +76283,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a5ccdd2c-0fa4-45e2-a986-571ffa658233" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f30d6940-85d6-4319-8658-7b5d199f76fb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D320D4CDE0E3CF4CAC53E9BAA4534025" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="25d2eab2951692af2de58fca8d59a9b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f30d6940-85d6-4319-8658-7b5d199f76fb" xmlns:ns3="a5ccdd2c-0fa4-45e2-a986-571ffa658233" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45d87c22090faa6df3c8e2be76bedf14" ns2:_="" ns3:_="">
     <xsd:import namespace="f30d6940-85d6-4319-8658-7b5d199f76fb"/>
@@ -76903,27 +76531,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEB5687-A511-489E-818B-D75BA96C26C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a5ccdd2c-0fa4-45e2-a986-571ffa658233"/>
+    <ds:schemaRef ds:uri="f30d6940-85d6-4319-8658-7b5d199f76fb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a5ccdd2c-0fa4-45e2-a986-571ffa658233" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f30d6940-85d6-4319-8658-7b5d199f76fb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6E9AEEC-7C7B-49A4-BC3A-CF23115A58E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA6C6C1-C134-46C1-AB67-8670CF0E614F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -76940,23 +76567,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6E9AEEC-7C7B-49A4-BC3A-CF23115A58E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEB5687-A511-489E-818B-D75BA96C26C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a5ccdd2c-0fa4-45e2-a986-571ffa658233"/>
-    <ds:schemaRef ds:uri="f30d6940-85d6-4319-8658-7b5d199f76fb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>